--- a/CATALOGO/catalogo_plantilla.xlsx
+++ b/CATALOGO/catalogo_plantilla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SUPERMERCADO ECOTODO\WEB\FIDELIZACION CLIENTE\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF79E3FE-1CE7-41DC-A0F9-3EA80F68882B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EED95A4-C85D-458C-A0A7-40897DB2260C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="186">
   <si>
     <t>ID</t>
   </si>
@@ -383,7 +383,7 @@
     <t>Mochila diseno Argentina</t>
   </si>
   <si>
-    <t>mochila arg.jpg.jpeg</t>
+    <t>mochila arg.png</t>
   </si>
   <si>
     <t>PRD-033</t>
@@ -470,15 +470,33 @@
     <t>yerbatero messi.jpg.jpeg</t>
   </si>
   <si>
+    <t>PRD-040</t>
+  </si>
+  <si>
+    <t>Remera Argentina</t>
+  </si>
+  <si>
+    <t>Remera seleccion Argentina edicion Super ECOtodo</t>
+  </si>
+  <si>
+    <t>remera arg eco.jpg</t>
+  </si>
+  <si>
     <t>⚙️ Super ECO todo — Configuración del Programa</t>
   </si>
   <si>
+    <t>PESOS COMPRA</t>
+  </si>
+  <si>
     <t>PUNTO</t>
   </si>
   <si>
     <t>PORCENTAJE</t>
   </si>
   <si>
+    <t>PESOS DE EQ</t>
+  </si>
+  <si>
     <t>10% mas de ptos por cp en efetivo</t>
   </si>
   <si>
@@ -561,12 +579,6 @@
   </si>
   <si>
     <t>Nombre del nivel máximo</t>
-  </si>
-  <si>
-    <t>PESOS DE EQ</t>
-  </si>
-  <si>
-    <t>PESOS COMPRA</t>
   </si>
 </sst>
 </file>
@@ -631,6 +643,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -740,11 +753,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -1048,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1931,7 +1944,9 @@
       <c r="C39" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="D39" s="10"/>
+      <c r="D39" s="10">
+        <v>30000</v>
+      </c>
       <c r="E39" s="10" t="s">
         <v>115</v>
       </c>
@@ -1941,7 +1956,7 @@
       </c>
       <c r="H39" s="10"/>
       <c r="I39" s="10" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -1954,7 +1969,9 @@
       <c r="C40" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D40" s="10"/>
+      <c r="D40" s="10">
+        <v>4000</v>
+      </c>
       <c r="E40" s="10" t="s">
         <v>115</v>
       </c>
@@ -1964,7 +1981,30 @@
       </c>
       <c r="H40" s="10"/>
       <c r="I40" s="10" t="s">
-        <v>15</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>149</v>
+      </c>
+      <c r="B41" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" t="s">
+        <v>151</v>
+      </c>
+      <c r="D41" s="9">
+        <v>15500</v>
+      </c>
+      <c r="E41" t="s">
+        <v>115</v>
+      </c>
+      <c r="G41" t="s">
+        <v>152</v>
+      </c>
+      <c r="I41" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1990,40 +2030,40 @@
   </cols>
   <sheetData>
     <row r="22" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
+      <c r="A22" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
       <c r="E22" s="2" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E23" s="1">
         <v>100</v>
@@ -2035,7 +2075,7 @@
       <c r="G23" s="1">
         <v>100</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="11">
         <v>0.01</v>
       </c>
       <c r="I23" s="1">
@@ -2049,13 +2089,13 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B24" s="4">
         <v>100</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E24" s="1">
         <v>15000</v>
@@ -2067,7 +2107,7 @@
       <c r="G24" s="1">
         <v>100</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="11">
         <v>0.01</v>
       </c>
       <c r="I24" s="1">
@@ -2081,13 +2121,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B25" s="4">
         <v>10000</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E25" s="1">
         <v>20000</v>
@@ -2099,7 +2139,7 @@
       <c r="G25" s="1">
         <v>100</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="11">
         <v>0.01</v>
       </c>
       <c r="I25" s="1">
@@ -2113,13 +2153,13 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B26" s="4">
         <v>20000</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E26" s="1">
         <v>45000</v>
@@ -2131,7 +2171,7 @@
       <c r="G26" s="1">
         <v>100</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="11">
         <v>0.01</v>
       </c>
       <c r="I26" s="1">
@@ -2145,13 +2185,13 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B27" s="4">
         <v>10</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E27" s="1">
         <v>50525.25</v>
@@ -2163,7 +2203,7 @@
       <c r="G27" s="1">
         <v>100</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="11">
         <v>0.01</v>
       </c>
       <c r="I27" s="1">
@@ -2177,13 +2217,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B28" s="4">
         <v>20</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E28" s="1">
         <v>50000</v>
@@ -2195,7 +2235,7 @@
       <c r="G28" s="1">
         <v>100</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="11">
         <v>0.01</v>
       </c>
       <c r="I28" s="1">
@@ -2209,13 +2249,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B29" s="4">
         <v>100</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E29" s="1">
         <v>60000</v>
@@ -2227,7 +2267,7 @@
       <c r="G29" s="1">
         <v>100</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="11">
         <v>0.01</v>
       </c>
       <c r="I29" s="1">
@@ -2241,13 +2281,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B30" s="4">
         <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E30" s="1">
         <v>70000</v>
@@ -2259,7 +2299,7 @@
       <c r="G30" s="1">
         <v>100</v>
       </c>
-      <c r="H30" s="13">
+      <c r="H30" s="11">
         <v>0.01</v>
       </c>
       <c r="I30" s="1">
@@ -2273,13 +2313,13 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E31" s="1">
         <v>80000</v>
@@ -2291,7 +2331,7 @@
       <c r="G31" s="1">
         <v>100</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H31" s="11">
         <v>0.01</v>
       </c>
       <c r="I31" s="1">
@@ -2305,13 +2345,13 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E32" s="1">
         <v>90000</v>
@@ -2323,7 +2363,7 @@
       <c r="G32" s="1">
         <v>100</v>
       </c>
-      <c r="H32" s="13">
+      <c r="H32" s="11">
         <v>0.01</v>
       </c>
       <c r="I32" s="1">
@@ -2337,13 +2377,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" ref="E33:E64" si="3">+E32+20000</f>
@@ -2356,7 +2396,7 @@
       <c r="G33" s="1">
         <v>100</v>
       </c>
-      <c r="H33" s="13">
+      <c r="H33" s="11">
         <v>0.01</v>
       </c>
       <c r="I33" s="1">
@@ -2380,7 +2420,7 @@
       <c r="G34" s="1">
         <v>100</v>
       </c>
-      <c r="H34" s="13">
+      <c r="H34" s="11">
         <v>0.01</v>
       </c>
       <c r="I34" s="1">
@@ -2404,7 +2444,7 @@
       <c r="G35" s="1">
         <v>100</v>
       </c>
-      <c r="H35" s="13">
+      <c r="H35" s="11">
         <v>0.01</v>
       </c>
       <c r="I35" s="1">
@@ -2428,7 +2468,7 @@
       <c r="G36" s="1">
         <v>100</v>
       </c>
-      <c r="H36" s="13">
+      <c r="H36" s="11">
         <v>0.01</v>
       </c>
       <c r="I36" s="1">
@@ -2452,7 +2492,7 @@
       <c r="G37" s="1">
         <v>100</v>
       </c>
-      <c r="H37" s="13">
+      <c r="H37" s="11">
         <v>0.01</v>
       </c>
       <c r="I37" s="1">
@@ -2476,7 +2516,7 @@
       <c r="G38" s="1">
         <v>100</v>
       </c>
-      <c r="H38" s="13">
+      <c r="H38" s="11">
         <v>0.01</v>
       </c>
       <c r="I38" s="1">
@@ -2500,7 +2540,7 @@
       <c r="G39" s="1">
         <v>100</v>
       </c>
-      <c r="H39" s="13">
+      <c r="H39" s="11">
         <v>0.01</v>
       </c>
       <c r="I39" s="1">
@@ -2524,7 +2564,7 @@
       <c r="G40" s="1">
         <v>100</v>
       </c>
-      <c r="H40" s="13">
+      <c r="H40" s="11">
         <v>0.01</v>
       </c>
       <c r="I40" s="1">
@@ -2548,7 +2588,7 @@
       <c r="G41" s="1">
         <v>100</v>
       </c>
-      <c r="H41" s="13">
+      <c r="H41" s="11">
         <v>0.01</v>
       </c>
       <c r="I41" s="1">
@@ -2572,7 +2612,7 @@
       <c r="G42" s="1">
         <v>100</v>
       </c>
-      <c r="H42" s="13">
+      <c r="H42" s="11">
         <v>0.01</v>
       </c>
       <c r="I42" s="1">
@@ -2596,7 +2636,7 @@
       <c r="G43" s="1">
         <v>100</v>
       </c>
-      <c r="H43" s="13">
+      <c r="H43" s="11">
         <v>0.01</v>
       </c>
       <c r="I43" s="1">
@@ -2620,7 +2660,7 @@
       <c r="G44" s="1">
         <v>100</v>
       </c>
-      <c r="H44" s="13">
+      <c r="H44" s="11">
         <v>0.01</v>
       </c>
       <c r="I44" s="1">
@@ -2644,7 +2684,7 @@
       <c r="G45" s="1">
         <v>100</v>
       </c>
-      <c r="H45" s="13">
+      <c r="H45" s="11">
         <v>0.01</v>
       </c>
       <c r="I45" s="1">
@@ -2668,7 +2708,7 @@
       <c r="G46" s="1">
         <v>100</v>
       </c>
-      <c r="H46" s="13">
+      <c r="H46" s="11">
         <v>0.01</v>
       </c>
       <c r="I46" s="1">
@@ -2692,7 +2732,7 @@
       <c r="G47" s="1">
         <v>100</v>
       </c>
-      <c r="H47" s="13">
+      <c r="H47" s="11">
         <v>0.01</v>
       </c>
       <c r="I47" s="1">
@@ -2716,7 +2756,7 @@
       <c r="G48" s="1">
         <v>100</v>
       </c>
-      <c r="H48" s="13">
+      <c r="H48" s="11">
         <v>0.01</v>
       </c>
       <c r="I48" s="1">
@@ -2740,7 +2780,7 @@
       <c r="G49" s="1">
         <v>100</v>
       </c>
-      <c r="H49" s="13">
+      <c r="H49" s="11">
         <v>0.01</v>
       </c>
       <c r="I49" s="1">
@@ -2764,7 +2804,7 @@
       <c r="G50" s="1">
         <v>100</v>
       </c>
-      <c r="H50" s="13">
+      <c r="H50" s="11">
         <v>0.01</v>
       </c>
       <c r="I50" s="1">
@@ -2788,7 +2828,7 @@
       <c r="G51" s="1">
         <v>100</v>
       </c>
-      <c r="H51" s="13">
+      <c r="H51" s="11">
         <v>0.01</v>
       </c>
       <c r="I51" s="1">
@@ -2812,7 +2852,7 @@
       <c r="G52" s="1">
         <v>100</v>
       </c>
-      <c r="H52" s="13">
+      <c r="H52" s="11">
         <v>0.01</v>
       </c>
       <c r="I52" s="1">
@@ -2836,7 +2876,7 @@
       <c r="G53" s="1">
         <v>100</v>
       </c>
-      <c r="H53" s="13">
+      <c r="H53" s="11">
         <v>0.01</v>
       </c>
       <c r="I53" s="1">
@@ -2860,7 +2900,7 @@
       <c r="G54" s="1">
         <v>100</v>
       </c>
-      <c r="H54" s="13">
+      <c r="H54" s="11">
         <v>0.01</v>
       </c>
       <c r="I54" s="1">
@@ -2884,7 +2924,7 @@
       <c r="G55" s="1">
         <v>100</v>
       </c>
-      <c r="H55" s="13">
+      <c r="H55" s="11">
         <v>0.01</v>
       </c>
       <c r="I55" s="1">
@@ -2908,7 +2948,7 @@
       <c r="G56" s="1">
         <v>100</v>
       </c>
-      <c r="H56" s="13">
+      <c r="H56" s="11">
         <v>0.01</v>
       </c>
       <c r="I56" s="1">
@@ -2932,7 +2972,7 @@
       <c r="G57" s="1">
         <v>100</v>
       </c>
-      <c r="H57" s="13">
+      <c r="H57" s="11">
         <v>0.01</v>
       </c>
       <c r="I57" s="1">
@@ -2956,7 +2996,7 @@
       <c r="G58" s="1">
         <v>100</v>
       </c>
-      <c r="H58" s="13">
+      <c r="H58" s="11">
         <v>0.01</v>
       </c>
       <c r="I58" s="1">
@@ -2980,7 +3020,7 @@
       <c r="G59" s="1">
         <v>100</v>
       </c>
-      <c r="H59" s="13">
+      <c r="H59" s="11">
         <v>0.01</v>
       </c>
       <c r="I59" s="1">
@@ -3004,7 +3044,7 @@
       <c r="G60" s="1">
         <v>100</v>
       </c>
-      <c r="H60" s="13">
+      <c r="H60" s="11">
         <v>0.01</v>
       </c>
       <c r="I60" s="1">
@@ -3028,7 +3068,7 @@
       <c r="G61" s="1">
         <v>100</v>
       </c>
-      <c r="H61" s="13">
+      <c r="H61" s="11">
         <v>0.01</v>
       </c>
       <c r="I61" s="1">
@@ -3052,7 +3092,7 @@
       <c r="G62" s="1">
         <v>100</v>
       </c>
-      <c r="H62" s="13">
+      <c r="H62" s="11">
         <v>0.01</v>
       </c>
       <c r="I62" s="1">
@@ -3076,7 +3116,7 @@
       <c r="G63" s="1">
         <v>100</v>
       </c>
-      <c r="H63" s="13">
+      <c r="H63" s="11">
         <v>0.01</v>
       </c>
       <c r="I63" s="1">
@@ -3100,7 +3140,7 @@
       <c r="G64" s="1">
         <v>100</v>
       </c>
-      <c r="H64" s="13">
+      <c r="H64" s="11">
         <v>0.01</v>
       </c>
       <c r="I64" s="1">
@@ -3124,7 +3164,7 @@
       <c r="G65" s="1">
         <v>100</v>
       </c>
-      <c r="H65" s="13">
+      <c r="H65" s="11">
         <v>0.01</v>
       </c>
       <c r="I65" s="1">
@@ -3148,7 +3188,7 @@
       <c r="G66" s="1">
         <v>100</v>
       </c>
-      <c r="H66" s="13">
+      <c r="H66" s="11">
         <v>0.01</v>
       </c>
       <c r="I66" s="1">
@@ -3172,7 +3212,7 @@
       <c r="G67" s="1">
         <v>100</v>
       </c>
-      <c r="H67" s="13">
+      <c r="H67" s="11">
         <v>0.01</v>
       </c>
       <c r="I67" s="1">
@@ -3196,7 +3236,7 @@
       <c r="G68" s="1">
         <v>100</v>
       </c>
-      <c r="H68" s="13">
+      <c r="H68" s="11">
         <v>0.01</v>
       </c>
       <c r="I68" s="1">
@@ -3220,7 +3260,7 @@
       <c r="G69" s="1">
         <v>100</v>
       </c>
-      <c r="H69" s="13">
+      <c r="H69" s="11">
         <v>0.01</v>
       </c>
       <c r="I69" s="1">
@@ -3244,7 +3284,7 @@
       <c r="G70" s="1">
         <v>100</v>
       </c>
-      <c r="H70" s="13">
+      <c r="H70" s="11">
         <v>0.01</v>
       </c>
       <c r="I70" s="1">
@@ -3268,7 +3308,7 @@
       <c r="G71" s="1">
         <v>100</v>
       </c>
-      <c r="H71" s="13">
+      <c r="H71" s="11">
         <v>0.01</v>
       </c>
       <c r="I71" s="1">
@@ -3292,7 +3332,7 @@
       <c r="G72" s="1">
         <v>100</v>
       </c>
-      <c r="H72" s="13">
+      <c r="H72" s="11">
         <v>0.01</v>
       </c>
       <c r="I72" s="1">
@@ -3316,7 +3356,7 @@
       <c r="G73" s="1">
         <v>100</v>
       </c>
-      <c r="H73" s="13">
+      <c r="H73" s="11">
         <v>0.01</v>
       </c>
       <c r="I73" s="1">
@@ -3340,7 +3380,7 @@
       <c r="G74" s="1">
         <v>100</v>
       </c>
-      <c r="H74" s="13">
+      <c r="H74" s="11">
         <v>0.01</v>
       </c>
       <c r="I74" s="1">
@@ -3364,7 +3404,7 @@
       <c r="G75" s="1">
         <v>100</v>
       </c>
-      <c r="H75" s="13">
+      <c r="H75" s="11">
         <v>0.01</v>
       </c>
       <c r="I75" s="1">
@@ -3388,7 +3428,7 @@
       <c r="G76" s="1">
         <v>100</v>
       </c>
-      <c r="H76" s="13">
+      <c r="H76" s="11">
         <v>0.01</v>
       </c>
       <c r="I76" s="1">
@@ -3412,7 +3452,7 @@
       <c r="G77" s="1">
         <v>100</v>
       </c>
-      <c r="H77" s="13">
+      <c r="H77" s="11">
         <v>0.01</v>
       </c>
       <c r="I77" s="1">
@@ -3436,7 +3476,7 @@
       <c r="G78" s="1">
         <v>100</v>
       </c>
-      <c r="H78" s="13">
+      <c r="H78" s="11">
         <v>0.01</v>
       </c>
       <c r="I78" s="1">
@@ -3460,7 +3500,7 @@
       <c r="G79" s="1">
         <v>100</v>
       </c>
-      <c r="H79" s="13">
+      <c r="H79" s="11">
         <v>0.01</v>
       </c>
       <c r="I79" s="1">
@@ -3484,7 +3524,7 @@
       <c r="G80" s="1">
         <v>100</v>
       </c>
-      <c r="H80" s="13">
+      <c r="H80" s="11">
         <v>0.01</v>
       </c>
       <c r="I80" s="1">
@@ -3508,7 +3548,7 @@
       <c r="G81" s="1">
         <v>100</v>
       </c>
-      <c r="H81" s="13">
+      <c r="H81" s="11">
         <v>0.01</v>
       </c>
       <c r="I81" s="1">
@@ -3532,7 +3572,7 @@
       <c r="G82" s="1">
         <v>100</v>
       </c>
-      <c r="H82" s="13">
+      <c r="H82" s="11">
         <v>0.01</v>
       </c>
       <c r="I82" s="1">
@@ -3556,7 +3596,7 @@
       <c r="G83" s="1">
         <v>100</v>
       </c>
-      <c r="H83" s="13">
+      <c r="H83" s="11">
         <v>0.01</v>
       </c>
       <c r="I83" s="1">
@@ -3580,7 +3620,7 @@
       <c r="G84" s="1">
         <v>100</v>
       </c>
-      <c r="H84" s="13">
+      <c r="H84" s="11">
         <v>0.01</v>
       </c>
       <c r="I84" s="1">
@@ -3604,7 +3644,7 @@
       <c r="G85" s="1">
         <v>100</v>
       </c>
-      <c r="H85" s="13">
+      <c r="H85" s="11">
         <v>0.01</v>
       </c>
       <c r="I85" s="1">
@@ -3628,7 +3668,7 @@
       <c r="G86" s="1">
         <v>100</v>
       </c>
-      <c r="H86" s="13">
+      <c r="H86" s="11">
         <v>0.01</v>
       </c>
       <c r="I86" s="1">
@@ -3652,7 +3692,7 @@
       <c r="G87" s="1">
         <v>100</v>
       </c>
-      <c r="H87" s="13">
+      <c r="H87" s="11">
         <v>0.01</v>
       </c>
       <c r="I87" s="1">
@@ -3676,7 +3716,7 @@
       <c r="G88" s="1">
         <v>100</v>
       </c>
-      <c r="H88" s="13">
+      <c r="H88" s="11">
         <v>0.01</v>
       </c>
       <c r="I88" s="1">
@@ -3700,7 +3740,7 @@
       <c r="G89" s="1">
         <v>100</v>
       </c>
-      <c r="H89" s="13">
+      <c r="H89" s="11">
         <v>0.01</v>
       </c>
       <c r="I89" s="1">
@@ -3724,7 +3764,7 @@
       <c r="G90" s="1">
         <v>100</v>
       </c>
-      <c r="H90" s="13">
+      <c r="H90" s="11">
         <v>0.01</v>
       </c>
       <c r="I90" s="1">
@@ -3748,7 +3788,7 @@
       <c r="G91" s="1">
         <v>100</v>
       </c>
-      <c r="H91" s="13">
+      <c r="H91" s="11">
         <v>0.01</v>
       </c>
       <c r="I91" s="1">
@@ -3772,7 +3812,7 @@
       <c r="G92" s="1">
         <v>100</v>
       </c>
-      <c r="H92" s="13">
+      <c r="H92" s="11">
         <v>0.01</v>
       </c>
       <c r="I92" s="1">
@@ -3796,7 +3836,7 @@
       <c r="G93" s="1">
         <v>100</v>
       </c>
-      <c r="H93" s="13">
+      <c r="H93" s="11">
         <v>0.01</v>
       </c>
       <c r="I93" s="1">
@@ -3820,7 +3860,7 @@
       <c r="G94" s="1">
         <v>100</v>
       </c>
-      <c r="H94" s="13">
+      <c r="H94" s="11">
         <v>0.01</v>
       </c>
       <c r="I94" s="1">
@@ -3844,7 +3884,7 @@
       <c r="G95" s="1">
         <v>100</v>
       </c>
-      <c r="H95" s="13">
+      <c r="H95" s="11">
         <v>0.01</v>
       </c>
       <c r="I95" s="1">
@@ -3868,7 +3908,7 @@
       <c r="G96" s="1">
         <v>100</v>
       </c>
-      <c r="H96" s="13">
+      <c r="H96" s="11">
         <v>0.01</v>
       </c>
       <c r="I96" s="1">
@@ -3892,7 +3932,7 @@
       <c r="G97" s="1">
         <v>100</v>
       </c>
-      <c r="H97" s="13">
+      <c r="H97" s="11">
         <v>0.01</v>
       </c>
       <c r="I97" s="1">
@@ -3916,7 +3956,7 @@
       <c r="G98" s="1">
         <v>100</v>
       </c>
-      <c r="H98" s="13">
+      <c r="H98" s="11">
         <v>0.01</v>
       </c>
       <c r="I98" s="1">
@@ -3940,7 +3980,7 @@
       <c r="G99" s="1">
         <v>100</v>
       </c>
-      <c r="H99" s="13">
+      <c r="H99" s="11">
         <v>0.01</v>
       </c>
       <c r="I99" s="1">
@@ -3964,7 +4004,7 @@
       <c r="G100" s="1">
         <v>100</v>
       </c>
-      <c r="H100" s="13">
+      <c r="H100" s="11">
         <v>0.01</v>
       </c>
       <c r="I100" s="1">
@@ -3988,7 +4028,7 @@
       <c r="G101" s="1">
         <v>100</v>
       </c>
-      <c r="H101" s="13">
+      <c r="H101" s="11">
         <v>0.01</v>
       </c>
       <c r="I101" s="1">
@@ -4012,7 +4052,7 @@
       <c r="G102" s="1">
         <v>100</v>
       </c>
-      <c r="H102" s="13">
+      <c r="H102" s="11">
         <v>0.01</v>
       </c>
       <c r="I102" s="1">
@@ -4036,7 +4076,7 @@
       <c r="G103" s="1">
         <v>100</v>
       </c>
-      <c r="H103" s="13">
+      <c r="H103" s="11">
         <v>0.01</v>
       </c>
       <c r="I103" s="1">
@@ -4060,7 +4100,7 @@
       <c r="G104" s="1">
         <v>100</v>
       </c>
-      <c r="H104" s="13">
+      <c r="H104" s="11">
         <v>0.01</v>
       </c>
       <c r="I104" s="1">
@@ -4084,7 +4124,7 @@
       <c r="G105" s="1">
         <v>100</v>
       </c>
-      <c r="H105" s="13">
+      <c r="H105" s="11">
         <v>0.01</v>
       </c>
       <c r="I105" s="1">
@@ -4108,7 +4148,7 @@
       <c r="G106" s="1">
         <v>100</v>
       </c>
-      <c r="H106" s="13">
+      <c r="H106" s="11">
         <v>0.01</v>
       </c>
       <c r="I106" s="1">
@@ -4132,7 +4172,7 @@
       <c r="G107" s="1">
         <v>100</v>
       </c>
-      <c r="H107" s="13">
+      <c r="H107" s="11">
         <v>0.01</v>
       </c>
       <c r="I107" s="1">
@@ -4156,7 +4196,7 @@
       <c r="G108" s="1">
         <v>100</v>
       </c>
-      <c r="H108" s="13">
+      <c r="H108" s="11">
         <v>0.01</v>
       </c>
       <c r="I108" s="1">
@@ -4180,7 +4220,7 @@
       <c r="G109" s="1">
         <v>100</v>
       </c>
-      <c r="H109" s="13">
+      <c r="H109" s="11">
         <v>0.01</v>
       </c>
       <c r="I109" s="1">
@@ -4204,7 +4244,7 @@
       <c r="G110" s="1">
         <v>100</v>
       </c>
-      <c r="H110" s="13">
+      <c r="H110" s="11">
         <v>0.01</v>
       </c>
       <c r="I110" s="1">
@@ -4228,7 +4268,7 @@
       <c r="G111" s="1">
         <v>100</v>
       </c>
-      <c r="H111" s="13">
+      <c r="H111" s="11">
         <v>0.01</v>
       </c>
       <c r="I111" s="1">
@@ -4252,7 +4292,7 @@
       <c r="G112" s="1">
         <v>100</v>
       </c>
-      <c r="H112" s="13">
+      <c r="H112" s="11">
         <v>0.01</v>
       </c>
       <c r="I112" s="1">
@@ -4276,7 +4316,7 @@
       <c r="G113" s="1">
         <v>100</v>
       </c>
-      <c r="H113" s="13">
+      <c r="H113" s="11">
         <v>0.01</v>
       </c>
       <c r="I113" s="1">
@@ -4300,7 +4340,7 @@
       <c r="G114" s="1">
         <v>100</v>
       </c>
-      <c r="H114" s="13">
+      <c r="H114" s="11">
         <v>0.01</v>
       </c>
       <c r="I114" s="1">
@@ -4324,7 +4364,7 @@
       <c r="G115" s="1">
         <v>100</v>
       </c>
-      <c r="H115" s="13">
+      <c r="H115" s="11">
         <v>0.01</v>
       </c>
       <c r="I115" s="1">
@@ -4348,7 +4388,7 @@
       <c r="G116" s="1">
         <v>100</v>
       </c>
-      <c r="H116" s="13">
+      <c r="H116" s="11">
         <v>0.01</v>
       </c>
       <c r="I116" s="1">
@@ -4372,7 +4412,7 @@
       <c r="G117" s="1">
         <v>100</v>
       </c>
-      <c r="H117" s="13">
+      <c r="H117" s="11">
         <v>0.01</v>
       </c>
       <c r="I117" s="1">
@@ -4396,7 +4436,7 @@
       <c r="G118" s="1">
         <v>100</v>
       </c>
-      <c r="H118" s="13">
+      <c r="H118" s="11">
         <v>0.01</v>
       </c>
       <c r="I118" s="1">
@@ -4420,7 +4460,7 @@
       <c r="G119" s="1">
         <v>100</v>
       </c>
-      <c r="H119" s="13">
+      <c r="H119" s="11">
         <v>0.01</v>
       </c>
       <c r="I119" s="1">
@@ -4444,7 +4484,7 @@
       <c r="G120" s="1">
         <v>100</v>
       </c>
-      <c r="H120" s="13">
+      <c r="H120" s="11">
         <v>0.01</v>
       </c>
       <c r="I120" s="1">
@@ -4468,7 +4508,7 @@
       <c r="G121" s="1">
         <v>100</v>
       </c>
-      <c r="H121" s="13">
+      <c r="H121" s="11">
         <v>0.01</v>
       </c>
       <c r="I121" s="1">
@@ -4492,7 +4532,7 @@
       <c r="G122" s="1">
         <v>100</v>
       </c>
-      <c r="H122" s="13">
+      <c r="H122" s="11">
         <v>0.01</v>
       </c>
       <c r="I122" s="1">
@@ -4516,7 +4556,7 @@
       <c r="G123" s="1">
         <v>100</v>
       </c>
-      <c r="H123" s="13">
+      <c r="H123" s="11">
         <v>0.01</v>
       </c>
       <c r="I123" s="1">
@@ -4540,7 +4580,7 @@
       <c r="G124" s="1">
         <v>100</v>
       </c>
-      <c r="H124" s="13">
+      <c r="H124" s="11">
         <v>0.01</v>
       </c>
       <c r="I124" s="1">
@@ -4564,7 +4604,7 @@
       <c r="G125" s="1">
         <v>100</v>
       </c>
-      <c r="H125" s="13">
+      <c r="H125" s="11">
         <v>0.01</v>
       </c>
       <c r="I125" s="1">
@@ -4588,7 +4628,7 @@
       <c r="G126" s="1">
         <v>100</v>
       </c>
-      <c r="H126" s="13">
+      <c r="H126" s="11">
         <v>0.01</v>
       </c>
       <c r="I126" s="1">
@@ -4612,7 +4652,7 @@
       <c r="G127" s="1">
         <v>100</v>
       </c>
-      <c r="H127" s="13">
+      <c r="H127" s="11">
         <v>0.01</v>
       </c>
       <c r="I127" s="1">
@@ -4636,7 +4676,7 @@
       <c r="G128" s="1">
         <v>100</v>
       </c>
-      <c r="H128" s="13">
+      <c r="H128" s="11">
         <v>0.01</v>
       </c>
       <c r="I128" s="1">
@@ -4660,7 +4700,7 @@
       <c r="G129" s="1">
         <v>100</v>
       </c>
-      <c r="H129" s="13">
+      <c r="H129" s="11">
         <v>0.01</v>
       </c>
       <c r="I129" s="1">
@@ -4684,7 +4724,7 @@
       <c r="G130" s="1">
         <v>100</v>
       </c>
-      <c r="H130" s="13">
+      <c r="H130" s="11">
         <v>0.01</v>
       </c>
       <c r="I130" s="1">
@@ -4708,7 +4748,7 @@
       <c r="G131" s="1">
         <v>100</v>
       </c>
-      <c r="H131" s="13">
+      <c r="H131" s="11">
         <v>0.01</v>
       </c>
       <c r="I131" s="1">
@@ -4732,7 +4772,7 @@
       <c r="G132" s="1">
         <v>100</v>
       </c>
-      <c r="H132" s="13">
+      <c r="H132" s="11">
         <v>0.01</v>
       </c>
       <c r="I132" s="1">
@@ -4756,7 +4796,7 @@
       <c r="G133" s="1">
         <v>100</v>
       </c>
-      <c r="H133" s="13">
+      <c r="H133" s="11">
         <v>0.01</v>
       </c>
       <c r="I133" s="1">
@@ -4780,7 +4820,7 @@
       <c r="G134" s="1">
         <v>100</v>
       </c>
-      <c r="H134" s="13">
+      <c r="H134" s="11">
         <v>0.01</v>
       </c>
       <c r="I134" s="1">
@@ -4804,7 +4844,7 @@
       <c r="G135" s="1">
         <v>100</v>
       </c>
-      <c r="H135" s="13">
+      <c r="H135" s="11">
         <v>0.01</v>
       </c>
       <c r="I135" s="1">
@@ -4828,7 +4868,7 @@
       <c r="G136" s="1">
         <v>100</v>
       </c>
-      <c r="H136" s="13">
+      <c r="H136" s="11">
         <v>0.01</v>
       </c>
       <c r="I136" s="1">
@@ -4852,7 +4892,7 @@
       <c r="G137" s="1">
         <v>100</v>
       </c>
-      <c r="H137" s="13">
+      <c r="H137" s="11">
         <v>0.01</v>
       </c>
       <c r="I137" s="1">
@@ -4876,7 +4916,7 @@
       <c r="G138" s="1">
         <v>100</v>
       </c>
-      <c r="H138" s="13">
+      <c r="H138" s="11">
         <v>0.01</v>
       </c>
       <c r="I138" s="1">
@@ -4900,7 +4940,7 @@
       <c r="G139" s="1">
         <v>100</v>
       </c>
-      <c r="H139" s="13">
+      <c r="H139" s="11">
         <v>0.01</v>
       </c>
       <c r="I139" s="1">
@@ -4924,7 +4964,7 @@
       <c r="G140" s="1">
         <v>100</v>
       </c>
-      <c r="H140" s="13">
+      <c r="H140" s="11">
         <v>0.01</v>
       </c>
       <c r="I140" s="1">
@@ -4948,7 +4988,7 @@
       <c r="G141" s="1">
         <v>100</v>
       </c>
-      <c r="H141" s="13">
+      <c r="H141" s="11">
         <v>0.01</v>
       </c>
       <c r="I141" s="1">
@@ -4972,7 +5012,7 @@
       <c r="G142" s="1">
         <v>100</v>
       </c>
-      <c r="H142" s="13">
+      <c r="H142" s="11">
         <v>0.01</v>
       </c>
       <c r="I142" s="1">
@@ -4996,7 +5036,7 @@
       <c r="G143" s="1">
         <v>100</v>
       </c>
-      <c r="H143" s="13">
+      <c r="H143" s="11">
         <v>0.01</v>
       </c>
       <c r="I143" s="1">
@@ -5020,7 +5060,7 @@
       <c r="G144" s="1">
         <v>100</v>
       </c>
-      <c r="H144" s="13">
+      <c r="H144" s="11">
         <v>0.01</v>
       </c>
       <c r="I144" s="1">
@@ -5044,7 +5084,7 @@
       <c r="G145" s="1">
         <v>100</v>
       </c>
-      <c r="H145" s="13">
+      <c r="H145" s="11">
         <v>0.01</v>
       </c>
       <c r="I145" s="1">
@@ -5068,7 +5108,7 @@
       <c r="G146" s="1">
         <v>100</v>
       </c>
-      <c r="H146" s="13">
+      <c r="H146" s="11">
         <v>0.01</v>
       </c>
       <c r="I146" s="1">
@@ -5092,7 +5132,7 @@
       <c r="G147" s="1">
         <v>100</v>
       </c>
-      <c r="H147" s="13">
+      <c r="H147" s="11">
         <v>0.01</v>
       </c>
       <c r="I147" s="1">
@@ -5116,7 +5156,7 @@
       <c r="G148" s="1">
         <v>100</v>
       </c>
-      <c r="H148" s="13">
+      <c r="H148" s="11">
         <v>0.01</v>
       </c>
       <c r="I148" s="1">
@@ -5140,7 +5180,7 @@
       <c r="G149" s="1">
         <v>100</v>
       </c>
-      <c r="H149" s="13">
+      <c r="H149" s="11">
         <v>0.01</v>
       </c>
       <c r="I149" s="1">
@@ -5164,7 +5204,7 @@
       <c r="G150" s="1">
         <v>100</v>
       </c>
-      <c r="H150" s="13">
+      <c r="H150" s="11">
         <v>0.01</v>
       </c>
       <c r="I150" s="1">
@@ -5188,7 +5228,7 @@
       <c r="G151" s="1">
         <v>100</v>
       </c>
-      <c r="H151" s="13">
+      <c r="H151" s="11">
         <v>0.01</v>
       </c>
       <c r="I151" s="1">
@@ -5212,7 +5252,7 @@
       <c r="G152" s="1">
         <v>100</v>
       </c>
-      <c r="H152" s="13">
+      <c r="H152" s="11">
         <v>0.01</v>
       </c>
       <c r="I152" s="1">
@@ -5236,7 +5276,7 @@
       <c r="G153" s="1">
         <v>100</v>
       </c>
-      <c r="H153" s="13">
+      <c r="H153" s="11">
         <v>0.01</v>
       </c>
       <c r="I153" s="1">
@@ -5260,7 +5300,7 @@
       <c r="G154" s="1">
         <v>100</v>
       </c>
-      <c r="H154" s="13">
+      <c r="H154" s="11">
         <v>0.01</v>
       </c>
       <c r="I154" s="1">
@@ -5284,7 +5324,7 @@
       <c r="G155" s="1">
         <v>100</v>
       </c>
-      <c r="H155" s="13">
+      <c r="H155" s="11">
         <v>0.01</v>
       </c>
       <c r="I155" s="1">
@@ -5308,7 +5348,7 @@
       <c r="G156" s="1">
         <v>100</v>
       </c>
-      <c r="H156" s="13">
+      <c r="H156" s="11">
         <v>0.01</v>
       </c>
       <c r="I156" s="1">
@@ -5332,7 +5372,7 @@
       <c r="G157" s="1">
         <v>100</v>
       </c>
-      <c r="H157" s="13">
+      <c r="H157" s="11">
         <v>0.01</v>
       </c>
       <c r="I157" s="1">
@@ -5356,7 +5396,7 @@
       <c r="G158" s="1">
         <v>100</v>
       </c>
-      <c r="H158" s="13">
+      <c r="H158" s="11">
         <v>0.01</v>
       </c>
       <c r="I158" s="1">
@@ -5380,7 +5420,7 @@
       <c r="G159" s="1">
         <v>100</v>
       </c>
-      <c r="H159" s="13">
+      <c r="H159" s="11">
         <v>0.01</v>
       </c>
       <c r="I159" s="1">
@@ -5404,7 +5444,7 @@
       <c r="G160" s="1">
         <v>100</v>
       </c>
-      <c r="H160" s="13">
+      <c r="H160" s="11">
         <v>0.01</v>
       </c>
       <c r="I160" s="1">
@@ -5428,7 +5468,7 @@
       <c r="G161" s="1">
         <v>100</v>
       </c>
-      <c r="H161" s="13">
+      <c r="H161" s="11">
         <v>0.01</v>
       </c>
       <c r="I161" s="1">
@@ -5452,7 +5492,7 @@
       <c r="G162" s="1">
         <v>100</v>
       </c>
-      <c r="H162" s="13">
+      <c r="H162" s="11">
         <v>0.01</v>
       </c>
       <c r="I162" s="1">
@@ -5476,7 +5516,7 @@
       <c r="G163" s="1">
         <v>100</v>
       </c>
-      <c r="H163" s="13">
+      <c r="H163" s="11">
         <v>0.01</v>
       </c>
       <c r="I163" s="1">
@@ -5500,7 +5540,7 @@
       <c r="G164" s="1">
         <v>100</v>
       </c>
-      <c r="H164" s="13">
+      <c r="H164" s="11">
         <v>0.01</v>
       </c>
       <c r="I164" s="1">
@@ -5524,7 +5564,7 @@
       <c r="G165" s="1">
         <v>100</v>
       </c>
-      <c r="H165" s="13">
+      <c r="H165" s="11">
         <v>0.01</v>
       </c>
       <c r="I165" s="1">
@@ -5548,7 +5588,7 @@
       <c r="G166" s="1">
         <v>100</v>
       </c>
-      <c r="H166" s="13">
+      <c r="H166" s="11">
         <v>0.01</v>
       </c>
       <c r="I166" s="1">
@@ -5572,7 +5612,7 @@
       <c r="G167" s="1">
         <v>100</v>
       </c>
-      <c r="H167" s="13">
+      <c r="H167" s="11">
         <v>0.01</v>
       </c>
       <c r="I167" s="1">
@@ -5596,7 +5636,7 @@
       <c r="G168" s="1">
         <v>100</v>
       </c>
-      <c r="H168" s="13">
+      <c r="H168" s="11">
         <v>0.01</v>
       </c>
       <c r="I168" s="1">
@@ -5620,7 +5660,7 @@
       <c r="G169" s="1">
         <v>100</v>
       </c>
-      <c r="H169" s="13">
+      <c r="H169" s="11">
         <v>0.01</v>
       </c>
       <c r="I169" s="1">
@@ -5644,7 +5684,7 @@
       <c r="G170" s="1">
         <v>100</v>
       </c>
-      <c r="H170" s="13">
+      <c r="H170" s="11">
         <v>0.01</v>
       </c>
       <c r="I170" s="1">
@@ -5668,7 +5708,7 @@
       <c r="G171" s="1">
         <v>100</v>
       </c>
-      <c r="H171" s="13">
+      <c r="H171" s="11">
         <v>0.01</v>
       </c>
       <c r="I171" s="1">
@@ -5692,7 +5732,7 @@
       <c r="G172" s="1">
         <v>100</v>
       </c>
-      <c r="H172" s="13">
+      <c r="H172" s="11">
         <v>0.01</v>
       </c>
       <c r="I172" s="1">
@@ -5716,7 +5756,7 @@
       <c r="G173" s="1">
         <v>100</v>
       </c>
-      <c r="H173" s="13">
+      <c r="H173" s="11">
         <v>0.01</v>
       </c>
       <c r="I173" s="1">
@@ -5740,7 +5780,7 @@
       <c r="G174" s="1">
         <v>100</v>
       </c>
-      <c r="H174" s="13">
+      <c r="H174" s="11">
         <v>0.01</v>
       </c>
       <c r="I174" s="1">
@@ -5764,7 +5804,7 @@
       <c r="G175" s="1">
         <v>100</v>
       </c>
-      <c r="H175" s="13">
+      <c r="H175" s="11">
         <v>0.01</v>
       </c>
       <c r="I175" s="1">
@@ -5788,7 +5828,7 @@
       <c r="G176" s="1">
         <v>100</v>
       </c>
-      <c r="H176" s="13">
+      <c r="H176" s="11">
         <v>0.01</v>
       </c>
       <c r="I176" s="1">
@@ -5812,7 +5852,7 @@
       <c r="G177" s="1">
         <v>100</v>
       </c>
-      <c r="H177" s="13">
+      <c r="H177" s="11">
         <v>0.01</v>
       </c>
       <c r="I177" s="1">
@@ -5836,7 +5876,7 @@
       <c r="G178" s="1">
         <v>100</v>
       </c>
-      <c r="H178" s="13">
+      <c r="H178" s="11">
         <v>0.01</v>
       </c>
       <c r="I178" s="1">
@@ -5860,7 +5900,7 @@
       <c r="G179" s="1">
         <v>100</v>
       </c>
-      <c r="H179" s="13">
+      <c r="H179" s="11">
         <v>0.01</v>
       </c>
       <c r="I179" s="1">
@@ -5884,7 +5924,7 @@
       <c r="G180" s="1">
         <v>100</v>
       </c>
-      <c r="H180" s="13">
+      <c r="H180" s="11">
         <v>0.01</v>
       </c>
       <c r="I180" s="1">
@@ -5908,7 +5948,7 @@
       <c r="G181" s="1">
         <v>100</v>
       </c>
-      <c r="H181" s="13">
+      <c r="H181" s="11">
         <v>0.01</v>
       </c>
       <c r="I181" s="1">
@@ -5932,7 +5972,7 @@
       <c r="G182" s="1">
         <v>100</v>
       </c>
-      <c r="H182" s="13">
+      <c r="H182" s="11">
         <v>0.01</v>
       </c>
       <c r="I182" s="1">
@@ -5956,7 +5996,7 @@
       <c r="G183" s="1">
         <v>100</v>
       </c>
-      <c r="H183" s="13">
+      <c r="H183" s="11">
         <v>0.01</v>
       </c>
       <c r="I183" s="1">
@@ -5980,7 +6020,7 @@
       <c r="G184" s="1">
         <v>100</v>
       </c>
-      <c r="H184" s="13">
+      <c r="H184" s="11">
         <v>0.01</v>
       </c>
       <c r="I184" s="1">
@@ -6004,7 +6044,7 @@
       <c r="G185" s="1">
         <v>100</v>
       </c>
-      <c r="H185" s="13">
+      <c r="H185" s="11">
         <v>0.01</v>
       </c>
       <c r="I185" s="1">
@@ -6028,7 +6068,7 @@
       <c r="G186" s="1">
         <v>100</v>
       </c>
-      <c r="H186" s="13">
+      <c r="H186" s="11">
         <v>0.01</v>
       </c>
       <c r="I186" s="1">
@@ -6052,7 +6092,7 @@
       <c r="G187" s="1">
         <v>100</v>
       </c>
-      <c r="H187" s="13">
+      <c r="H187" s="11">
         <v>0.01</v>
       </c>
       <c r="I187" s="1">
@@ -6076,7 +6116,7 @@
       <c r="G188" s="1">
         <v>100</v>
       </c>
-      <c r="H188" s="13">
+      <c r="H188" s="11">
         <v>0.01</v>
       </c>
       <c r="I188" s="1">
@@ -6100,7 +6140,7 @@
       <c r="G189" s="1">
         <v>100</v>
       </c>
-      <c r="H189" s="13">
+      <c r="H189" s="11">
         <v>0.01</v>
       </c>
       <c r="I189" s="1">
@@ -6124,7 +6164,7 @@
       <c r="G190" s="1">
         <v>100</v>
       </c>
-      <c r="H190" s="13">
+      <c r="H190" s="11">
         <v>0.01</v>
       </c>
       <c r="I190" s="1">
@@ -6148,7 +6188,7 @@
       <c r="G191" s="1">
         <v>100</v>
       </c>
-      <c r="H191" s="13">
+      <c r="H191" s="11">
         <v>0.01</v>
       </c>
       <c r="I191" s="1">
@@ -6172,7 +6212,7 @@
       <c r="G192" s="1">
         <v>100</v>
       </c>
-      <c r="H192" s="13">
+      <c r="H192" s="11">
         <v>0.01</v>
       </c>
       <c r="I192" s="1">
@@ -6196,7 +6236,7 @@
       <c r="G193" s="1">
         <v>100</v>
       </c>
-      <c r="H193" s="13">
+      <c r="H193" s="11">
         <v>0.01</v>
       </c>
       <c r="I193" s="1">
@@ -6220,7 +6260,7 @@
       <c r="G194" s="1">
         <v>100</v>
       </c>
-      <c r="H194" s="13">
+      <c r="H194" s="11">
         <v>0.01</v>
       </c>
       <c r="I194" s="1">
@@ -6244,7 +6284,7 @@
       <c r="G195" s="1">
         <v>100</v>
       </c>
-      <c r="H195" s="13">
+      <c r="H195" s="11">
         <v>0.01</v>
       </c>
       <c r="I195" s="1">
@@ -6268,7 +6308,7 @@
       <c r="G196" s="1">
         <v>100</v>
       </c>
-      <c r="H196" s="13">
+      <c r="H196" s="11">
         <v>0.01</v>
       </c>
       <c r="I196" s="1">
@@ -6292,7 +6332,7 @@
       <c r="G197" s="1">
         <v>100</v>
       </c>
-      <c r="H197" s="13">
+      <c r="H197" s="11">
         <v>0.01</v>
       </c>
       <c r="I197" s="1">
@@ -6316,7 +6356,7 @@
       <c r="G198" s="1">
         <v>100</v>
       </c>
-      <c r="H198" s="13">
+      <c r="H198" s="11">
         <v>0.01</v>
       </c>
       <c r="I198" s="1">
@@ -6340,7 +6380,7 @@
       <c r="G199" s="1">
         <v>100</v>
       </c>
-      <c r="H199" s="13">
+      <c r="H199" s="11">
         <v>0.01</v>
       </c>
       <c r="I199" s="1">
@@ -6364,7 +6404,7 @@
       <c r="G200" s="1">
         <v>100</v>
       </c>
-      <c r="H200" s="13">
+      <c r="H200" s="11">
         <v>0.01</v>
       </c>
       <c r="I200" s="1">
@@ -6388,7 +6428,7 @@
       <c r="G201" s="1">
         <v>100</v>
       </c>
-      <c r="H201" s="13">
+      <c r="H201" s="11">
         <v>0.01</v>
       </c>
       <c r="I201" s="1">
@@ -6412,7 +6452,7 @@
       <c r="G202" s="1">
         <v>100</v>
       </c>
-      <c r="H202" s="13">
+      <c r="H202" s="11">
         <v>0.01</v>
       </c>
       <c r="I202" s="1">
@@ -6436,7 +6476,7 @@
       <c r="G203" s="1">
         <v>100</v>
       </c>
-      <c r="H203" s="13">
+      <c r="H203" s="11">
         <v>0.01</v>
       </c>
       <c r="I203" s="1">
@@ -6460,7 +6500,7 @@
       <c r="G204" s="1">
         <v>100</v>
       </c>
-      <c r="H204" s="13">
+      <c r="H204" s="11">
         <v>0.01</v>
       </c>
       <c r="I204" s="1">
@@ -6484,7 +6524,7 @@
       <c r="G205" s="1">
         <v>100</v>
       </c>
-      <c r="H205" s="13">
+      <c r="H205" s="11">
         <v>0.01</v>
       </c>
       <c r="I205" s="1">
@@ -6508,7 +6548,7 @@
       <c r="G206" s="1">
         <v>100</v>
       </c>
-      <c r="H206" s="13">
+      <c r="H206" s="11">
         <v>0.01</v>
       </c>
       <c r="I206" s="1">
@@ -6532,7 +6572,7 @@
       <c r="G207" s="1">
         <v>100</v>
       </c>
-      <c r="H207" s="13">
+      <c r="H207" s="11">
         <v>0.01</v>
       </c>
       <c r="I207" s="1">
@@ -6546,7 +6586,7 @@
     </row>
     <row r="208" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E208" s="1">
-        <f t="shared" ref="E208:E227" si="15">+E207+100000</f>
+        <f t="shared" ref="E208:E239" si="15">+E207+100000</f>
         <v>4250000</v>
       </c>
       <c r="F208" s="1">
@@ -6556,7 +6596,7 @@
       <c r="G208" s="1">
         <v>100</v>
       </c>
-      <c r="H208" s="13">
+      <c r="H208" s="11">
         <v>0.01</v>
       </c>
       <c r="I208" s="1">
@@ -6580,7 +6620,7 @@
       <c r="G209" s="1">
         <v>100</v>
       </c>
-      <c r="H209" s="13">
+      <c r="H209" s="11">
         <v>0.01</v>
       </c>
       <c r="I209" s="1">
@@ -6604,7 +6644,7 @@
       <c r="G210" s="1">
         <v>100</v>
       </c>
-      <c r="H210" s="13">
+      <c r="H210" s="11">
         <v>0.01</v>
       </c>
       <c r="I210" s="1">
@@ -6628,7 +6668,7 @@
       <c r="G211" s="1">
         <v>100</v>
       </c>
-      <c r="H211" s="13">
+      <c r="H211" s="11">
         <v>0.01</v>
       </c>
       <c r="I211" s="1">
@@ -6652,7 +6692,7 @@
       <c r="G212" s="1">
         <v>100</v>
       </c>
-      <c r="H212" s="13">
+      <c r="H212" s="11">
         <v>0.01</v>
       </c>
       <c r="I212" s="1">
@@ -6676,7 +6716,7 @@
       <c r="G213" s="1">
         <v>100</v>
       </c>
-      <c r="H213" s="13">
+      <c r="H213" s="11">
         <v>0.01</v>
       </c>
       <c r="I213" s="1">
@@ -6700,7 +6740,7 @@
       <c r="G214" s="1">
         <v>100</v>
       </c>
-      <c r="H214" s="13">
+      <c r="H214" s="11">
         <v>0.01</v>
       </c>
       <c r="I214" s="1">
@@ -6718,21 +6758,21 @@
         <v>4950000</v>
       </c>
       <c r="F215" s="1">
-        <f t="shared" ref="F215:F278" si="16">+E215/G215</f>
+        <f t="shared" ref="F215:F265" si="16">+E215/G215</f>
         <v>49500</v>
       </c>
       <c r="G215" s="1">
         <v>100</v>
       </c>
-      <c r="H215" s="13">
+      <c r="H215" s="11">
         <v>0.01</v>
       </c>
       <c r="I215" s="1">
-        <f t="shared" ref="I215:I278" si="17">+H215*E215</f>
+        <f t="shared" ref="I215:I265" si="17">+H215*E215</f>
         <v>49500</v>
       </c>
       <c r="J215" s="1">
-        <f t="shared" ref="J215:J227" si="18">+F215*1.1</f>
+        <f t="shared" ref="J215:J265" si="18">+F215*1.1</f>
         <v>54450.000000000007</v>
       </c>
     </row>
@@ -6748,7 +6788,7 @@
       <c r="G216" s="1">
         <v>100</v>
       </c>
-      <c r="H216" s="13">
+      <c r="H216" s="11">
         <v>0.01</v>
       </c>
       <c r="I216" s="1">
@@ -6772,7 +6812,7 @@
       <c r="G217" s="1">
         <v>100</v>
       </c>
-      <c r="H217" s="13">
+      <c r="H217" s="11">
         <v>0.01</v>
       </c>
       <c r="I217" s="1">
@@ -6796,7 +6836,7 @@
       <c r="G218" s="1">
         <v>100</v>
       </c>
-      <c r="H218" s="13">
+      <c r="H218" s="11">
         <v>0.01</v>
       </c>
       <c r="I218" s="1">
@@ -6820,7 +6860,7 @@
       <c r="G219" s="1">
         <v>100</v>
       </c>
-      <c r="H219" s="13">
+      <c r="H219" s="11">
         <v>0.01</v>
       </c>
       <c r="I219" s="1">
@@ -6844,7 +6884,7 @@
       <c r="G220" s="1">
         <v>100</v>
       </c>
-      <c r="H220" s="13">
+      <c r="H220" s="11">
         <v>0.01</v>
       </c>
       <c r="I220" s="1">
@@ -6868,7 +6908,7 @@
       <c r="G221" s="1">
         <v>100</v>
       </c>
-      <c r="H221" s="13">
+      <c r="H221" s="11">
         <v>0.01</v>
       </c>
       <c r="I221" s="1">
@@ -6892,7 +6932,7 @@
       <c r="G222" s="1">
         <v>100</v>
       </c>
-      <c r="H222" s="13">
+      <c r="H222" s="11">
         <v>0.01</v>
       </c>
       <c r="I222" s="1">
@@ -6916,7 +6956,7 @@
       <c r="G223" s="1">
         <v>100</v>
       </c>
-      <c r="H223" s="13">
+      <c r="H223" s="11">
         <v>0.01</v>
       </c>
       <c r="I223" s="1">
@@ -6940,7 +6980,7 @@
       <c r="G224" s="1">
         <v>100</v>
       </c>
-      <c r="H224" s="13">
+      <c r="H224" s="11">
         <v>0.01</v>
       </c>
       <c r="I224" s="1">
@@ -6964,7 +7004,7 @@
       <c r="G225" s="1">
         <v>100</v>
       </c>
-      <c r="H225" s="13">
+      <c r="H225" s="11">
         <v>0.01</v>
       </c>
       <c r="I225" s="1">
@@ -6988,7 +7028,7 @@
       <c r="G226" s="1">
         <v>100</v>
       </c>
-      <c r="H226" s="13">
+      <c r="H226" s="11">
         <v>0.01</v>
       </c>
       <c r="I226" s="1">
@@ -7012,7 +7052,7 @@
       <c r="G227" s="1">
         <v>100</v>
       </c>
-      <c r="H227" s="13">
+      <c r="H227" s="11">
         <v>0.01</v>
       </c>
       <c r="I227" s="1">
@@ -7026,7 +7066,7 @@
     </row>
     <row r="228" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E228" s="1">
-        <f t="shared" ref="E228:E265" si="19">+E227+100000</f>
+        <f t="shared" si="15"/>
         <v>6250000</v>
       </c>
       <c r="F228" s="1">
@@ -7036,21 +7076,21 @@
       <c r="G228" s="1">
         <v>100</v>
       </c>
-      <c r="H228" s="13">
+      <c r="H228" s="11">
         <v>0.01</v>
       </c>
       <c r="I228" s="1">
-        <f t="shared" ref="I228:I265" si="20">+H228*E228</f>
+        <f t="shared" si="17"/>
         <v>62500</v>
       </c>
       <c r="J228" s="1">
-        <f t="shared" ref="J228:J265" si="21">+F228*1.1</f>
+        <f t="shared" si="18"/>
         <v>68750</v>
       </c>
     </row>
     <row r="229" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E229" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>6350000</v>
       </c>
       <c r="F229" s="1">
@@ -7060,21 +7100,21 @@
       <c r="G229" s="1">
         <v>100</v>
       </c>
-      <c r="H229" s="13">
+      <c r="H229" s="11">
         <v>0.01</v>
       </c>
       <c r="I229" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>63500</v>
       </c>
       <c r="J229" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>69850</v>
       </c>
     </row>
     <row r="230" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E230" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>6450000</v>
       </c>
       <c r="F230" s="1">
@@ -7084,21 +7124,21 @@
       <c r="G230" s="1">
         <v>100</v>
       </c>
-      <c r="H230" s="13">
+      <c r="H230" s="11">
         <v>0.01</v>
       </c>
       <c r="I230" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>64500</v>
       </c>
       <c r="J230" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>70950</v>
       </c>
     </row>
     <row r="231" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E231" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>6550000</v>
       </c>
       <c r="F231" s="1">
@@ -7108,21 +7148,21 @@
       <c r="G231" s="1">
         <v>100</v>
       </c>
-      <c r="H231" s="13">
+      <c r="H231" s="11">
         <v>0.01</v>
       </c>
       <c r="I231" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>65500</v>
       </c>
       <c r="J231" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>72050</v>
       </c>
     </row>
     <row r="232" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E232" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>6650000</v>
       </c>
       <c r="F232" s="1">
@@ -7132,21 +7172,21 @@
       <c r="G232" s="1">
         <v>100</v>
       </c>
-      <c r="H232" s="13">
+      <c r="H232" s="11">
         <v>0.01</v>
       </c>
       <c r="I232" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>66500</v>
       </c>
       <c r="J232" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>73150</v>
       </c>
     </row>
     <row r="233" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E233" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>6750000</v>
       </c>
       <c r="F233" s="1">
@@ -7156,21 +7196,21 @@
       <c r="G233" s="1">
         <v>100</v>
       </c>
-      <c r="H233" s="13">
+      <c r="H233" s="11">
         <v>0.01</v>
       </c>
       <c r="I233" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>67500</v>
       </c>
       <c r="J233" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>74250</v>
       </c>
     </row>
     <row r="234" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E234" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>6850000</v>
       </c>
       <c r="F234" s="1">
@@ -7180,21 +7220,21 @@
       <c r="G234" s="1">
         <v>100</v>
       </c>
-      <c r="H234" s="13">
+      <c r="H234" s="11">
         <v>0.01</v>
       </c>
       <c r="I234" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>68500</v>
       </c>
       <c r="J234" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>75350</v>
       </c>
     </row>
     <row r="235" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E235" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>6950000</v>
       </c>
       <c r="F235" s="1">
@@ -7204,21 +7244,21 @@
       <c r="G235" s="1">
         <v>100</v>
       </c>
-      <c r="H235" s="13">
+      <c r="H235" s="11">
         <v>0.01</v>
       </c>
       <c r="I235" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>69500</v>
       </c>
       <c r="J235" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>76450</v>
       </c>
     </row>
     <row r="236" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E236" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>7050000</v>
       </c>
       <c r="F236" s="1">
@@ -7228,21 +7268,21 @@
       <c r="G236" s="1">
         <v>100</v>
       </c>
-      <c r="H236" s="13">
+      <c r="H236" s="11">
         <v>0.01</v>
       </c>
       <c r="I236" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>70500</v>
       </c>
       <c r="J236" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>77550</v>
       </c>
     </row>
     <row r="237" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E237" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>7150000</v>
       </c>
       <c r="F237" s="1">
@@ -7252,21 +7292,21 @@
       <c r="G237" s="1">
         <v>100</v>
       </c>
-      <c r="H237" s="13">
+      <c r="H237" s="11">
         <v>0.01</v>
       </c>
       <c r="I237" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>71500</v>
       </c>
       <c r="J237" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>78650</v>
       </c>
     </row>
     <row r="238" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E238" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>7250000</v>
       </c>
       <c r="F238" s="1">
@@ -7276,21 +7316,21 @@
       <c r="G238" s="1">
         <v>100</v>
       </c>
-      <c r="H238" s="13">
+      <c r="H238" s="11">
         <v>0.01</v>
       </c>
       <c r="I238" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>72500</v>
       </c>
       <c r="J238" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>79750</v>
       </c>
     </row>
     <row r="239" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E239" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>7350000</v>
       </c>
       <c r="F239" s="1">
@@ -7300,21 +7340,21 @@
       <c r="G239" s="1">
         <v>100</v>
       </c>
-      <c r="H239" s="13">
+      <c r="H239" s="11">
         <v>0.01</v>
       </c>
       <c r="I239" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>73500</v>
       </c>
       <c r="J239" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>80850</v>
       </c>
     </row>
     <row r="240" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E240" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="E240:E265" si="19">+E239+100000</f>
         <v>7450000</v>
       </c>
       <c r="F240" s="1">
@@ -7324,15 +7364,15 @@
       <c r="G240" s="1">
         <v>100</v>
       </c>
-      <c r="H240" s="13">
+      <c r="H240" s="11">
         <v>0.01</v>
       </c>
       <c r="I240" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>74500</v>
       </c>
       <c r="J240" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>81950</v>
       </c>
     </row>
@@ -7348,15 +7388,15 @@
       <c r="G241" s="1">
         <v>100</v>
       </c>
-      <c r="H241" s="13">
+      <c r="H241" s="11">
         <v>0.01</v>
       </c>
       <c r="I241" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>75500</v>
       </c>
       <c r="J241" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>83050</v>
       </c>
     </row>
@@ -7372,15 +7412,15 @@
       <c r="G242" s="1">
         <v>100</v>
       </c>
-      <c r="H242" s="13">
+      <c r="H242" s="11">
         <v>0.01</v>
       </c>
       <c r="I242" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>76500</v>
       </c>
       <c r="J242" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>84150</v>
       </c>
     </row>
@@ -7396,15 +7436,15 @@
       <c r="G243" s="1">
         <v>100</v>
       </c>
-      <c r="H243" s="13">
+      <c r="H243" s="11">
         <v>0.01</v>
       </c>
       <c r="I243" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>77500</v>
       </c>
       <c r="J243" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>85250</v>
       </c>
     </row>
@@ -7420,15 +7460,15 @@
       <c r="G244" s="1">
         <v>100</v>
       </c>
-      <c r="H244" s="13">
+      <c r="H244" s="11">
         <v>0.01</v>
       </c>
       <c r="I244" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>78500</v>
       </c>
       <c r="J244" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>86350</v>
       </c>
     </row>
@@ -7444,15 +7484,15 @@
       <c r="G245" s="1">
         <v>100</v>
       </c>
-      <c r="H245" s="13">
+      <c r="H245" s="11">
         <v>0.01</v>
       </c>
       <c r="I245" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>79500</v>
       </c>
       <c r="J245" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>87450</v>
       </c>
     </row>
@@ -7468,15 +7508,15 @@
       <c r="G246" s="1">
         <v>100</v>
       </c>
-      <c r="H246" s="13">
+      <c r="H246" s="11">
         <v>0.01</v>
       </c>
       <c r="I246" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>80500</v>
       </c>
       <c r="J246" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>88550</v>
       </c>
     </row>
@@ -7492,15 +7532,15 @@
       <c r="G247" s="1">
         <v>100</v>
       </c>
-      <c r="H247" s="13">
+      <c r="H247" s="11">
         <v>0.01</v>
       </c>
       <c r="I247" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>81500</v>
       </c>
       <c r="J247" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>89650</v>
       </c>
     </row>
@@ -7516,15 +7556,15 @@
       <c r="G248" s="1">
         <v>100</v>
       </c>
-      <c r="H248" s="13">
+      <c r="H248" s="11">
         <v>0.01</v>
       </c>
       <c r="I248" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>82500</v>
       </c>
       <c r="J248" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>90750.000000000015</v>
       </c>
     </row>
@@ -7540,15 +7580,15 @@
       <c r="G249" s="1">
         <v>100</v>
       </c>
-      <c r="H249" s="13">
+      <c r="H249" s="11">
         <v>0.01</v>
       </c>
       <c r="I249" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>83500</v>
       </c>
       <c r="J249" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>91850.000000000015</v>
       </c>
     </row>
@@ -7564,15 +7604,15 @@
       <c r="G250" s="1">
         <v>100</v>
       </c>
-      <c r="H250" s="13">
+      <c r="H250" s="11">
         <v>0.01</v>
       </c>
       <c r="I250" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>84500</v>
       </c>
       <c r="J250" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>92950.000000000015</v>
       </c>
     </row>
@@ -7588,15 +7628,15 @@
       <c r="G251" s="1">
         <v>100</v>
       </c>
-      <c r="H251" s="13">
+      <c r="H251" s="11">
         <v>0.01</v>
       </c>
       <c r="I251" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>85500</v>
       </c>
       <c r="J251" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>94050.000000000015</v>
       </c>
     </row>
@@ -7612,15 +7652,15 @@
       <c r="G252" s="1">
         <v>100</v>
       </c>
-      <c r="H252" s="13">
+      <c r="H252" s="11">
         <v>0.01</v>
       </c>
       <c r="I252" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>86500</v>
       </c>
       <c r="J252" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>95150.000000000015</v>
       </c>
     </row>
@@ -7636,15 +7676,15 @@
       <c r="G253" s="1">
         <v>100</v>
       </c>
-      <c r="H253" s="13">
+      <c r="H253" s="11">
         <v>0.01</v>
       </c>
       <c r="I253" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>87500</v>
       </c>
       <c r="J253" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>96250.000000000015</v>
       </c>
     </row>
@@ -7660,15 +7700,15 @@
       <c r="G254" s="1">
         <v>100</v>
       </c>
-      <c r="H254" s="13">
+      <c r="H254" s="11">
         <v>0.01</v>
       </c>
       <c r="I254" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>88500</v>
       </c>
       <c r="J254" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>97350.000000000015</v>
       </c>
     </row>
@@ -7684,15 +7724,15 @@
       <c r="G255" s="1">
         <v>100</v>
       </c>
-      <c r="H255" s="13">
+      <c r="H255" s="11">
         <v>0.01</v>
       </c>
       <c r="I255" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>89500</v>
       </c>
       <c r="J255" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>98450.000000000015</v>
       </c>
     </row>
@@ -7708,15 +7748,15 @@
       <c r="G256" s="1">
         <v>100</v>
       </c>
-      <c r="H256" s="13">
+      <c r="H256" s="11">
         <v>0.01</v>
       </c>
       <c r="I256" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>90500</v>
       </c>
       <c r="J256" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>99550.000000000015</v>
       </c>
     </row>
@@ -7732,15 +7772,15 @@
       <c r="G257" s="1">
         <v>100</v>
       </c>
-      <c r="H257" s="13">
+      <c r="H257" s="11">
         <v>0.01</v>
       </c>
       <c r="I257" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>91500</v>
       </c>
       <c r="J257" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>100650.00000000001</v>
       </c>
     </row>
@@ -7756,15 +7796,15 @@
       <c r="G258" s="1">
         <v>100</v>
       </c>
-      <c r="H258" s="13">
+      <c r="H258" s="11">
         <v>0.01</v>
       </c>
       <c r="I258" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>92500</v>
       </c>
       <c r="J258" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>101750.00000000001</v>
       </c>
     </row>
@@ -7780,15 +7820,15 @@
       <c r="G259" s="1">
         <v>100</v>
       </c>
-      <c r="H259" s="13">
+      <c r="H259" s="11">
         <v>0.01</v>
       </c>
       <c r="I259" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>93500</v>
       </c>
       <c r="J259" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>102850.00000000001</v>
       </c>
     </row>
@@ -7804,15 +7844,15 @@
       <c r="G260" s="1">
         <v>100</v>
       </c>
-      <c r="H260" s="13">
+      <c r="H260" s="11">
         <v>0.01</v>
       </c>
       <c r="I260" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>94500</v>
       </c>
       <c r="J260" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>103950.00000000001</v>
       </c>
     </row>
@@ -7828,15 +7868,15 @@
       <c r="G261" s="1">
         <v>100</v>
       </c>
-      <c r="H261" s="13">
+      <c r="H261" s="11">
         <v>0.01</v>
       </c>
       <c r="I261" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>95500</v>
       </c>
       <c r="J261" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>105050.00000000001</v>
       </c>
     </row>
@@ -7852,15 +7892,15 @@
       <c r="G262" s="1">
         <v>100</v>
       </c>
-      <c r="H262" s="13">
+      <c r="H262" s="11">
         <v>0.01</v>
       </c>
       <c r="I262" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>96500</v>
       </c>
       <c r="J262" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>106150.00000000001</v>
       </c>
     </row>
@@ -7876,15 +7916,15 @@
       <c r="G263" s="1">
         <v>100</v>
       </c>
-      <c r="H263" s="13">
+      <c r="H263" s="11">
         <v>0.01</v>
       </c>
       <c r="I263" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>97500</v>
       </c>
       <c r="J263" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>107250.00000000001</v>
       </c>
     </row>
@@ -7900,15 +7940,15 @@
       <c r="G264" s="1">
         <v>100</v>
       </c>
-      <c r="H264" s="13">
+      <c r="H264" s="11">
         <v>0.01</v>
       </c>
       <c r="I264" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>98500</v>
       </c>
       <c r="J264" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>108350.00000000001</v>
       </c>
     </row>
@@ -7924,15 +7964,15 @@
       <c r="G265" s="1">
         <v>100</v>
       </c>
-      <c r="H265" s="13">
+      <c r="H265" s="11">
         <v>0.01</v>
       </c>
       <c r="I265" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>99500</v>
       </c>
       <c r="J265" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>109450.00000000001</v>
       </c>
     </row>
